--- a/numerical-workflows/v2/framework/04_数值文档/节奏/主角等级_数值文档.xlsx
+++ b/numerical-workflows/v2/framework/04_数值文档/节奏/主角等级_数值文档.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="主角等级_单源" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主角等级_单源" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,13 +501,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>80</v>
@@ -714,7 +714,7 @@
         <v>170</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1250</v>
@@ -731,16 +731,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1450</v>
+        <v>1430</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -757,13 +757,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1680</v>
+        <v>1640</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>30</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1940</v>
+        <v>1880</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -803,13 +803,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2230</v>
+        <v>2150</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -826,13 +826,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2550</v>
+        <v>2450</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -846,16 +846,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2920</v>
+        <v>2780</v>
       </c>
       <c r="F20" t="n">
         <v>2</v>
@@ -872,13 +872,13 @@
         <v>50</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3340</v>
+        <v>3160</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
@@ -895,13 +895,13 @@
         <v>50</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>3810</v>
+        <v>3590</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -918,13 +918,13 @@
         <v>50</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4330</v>
+        <v>4070</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -938,16 +938,16 @@
         <v>20</v>
       </c>
       <c r="B24" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1120</v>
+        <v>530</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5450</v>
+        <v>4600</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -961,16 +961,16 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1220</v>
+        <v>1130</v>
       </c>
       <c r="D25" t="n">
         <v>15</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6670</v>
+        <v>5730</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -987,13 +987,13 @@
         <v>100</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1320</v>
+        <v>1230</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7990</v>
+        <v>6960</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -1010,13 +1010,13 @@
         <v>100</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1420</v>
+        <v>1330</v>
       </c>
       <c r="D27" t="n">
         <v>15</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>9410</v>
+        <v>8290</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -1033,13 +1033,13 @@
         <v>100</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1520</v>
+        <v>1430</v>
       </c>
       <c r="D28" t="n">
         <v>15</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>10930</v>
+        <v>9720</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -1056,13 +1056,13 @@
         <v>100</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1620</v>
+        <v>1530</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>12550</v>
+        <v>11250</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -1079,13 +1079,13 @@
         <v>100</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1720</v>
+        <v>1630</v>
       </c>
       <c r="D30" t="n">
         <v>15</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14270</v>
+        <v>12880</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -1102,13 +1102,13 @@
         <v>100</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1820</v>
+        <v>1730</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>16090</v>
+        <v>14610</v>
       </c>
       <c r="F31" t="n">
         <v>4</v>
@@ -1125,13 +1125,13 @@
         <v>100</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1920</v>
+        <v>1830</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>18010</v>
+        <v>16440</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -1148,13 +1148,13 @@
         <v>100</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2020</v>
+        <v>1930</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>20030</v>
+        <v>18370</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -1171,13 +1171,13 @@
         <v>100</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2120</v>
+        <v>2030</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>22150</v>
+        <v>20400</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -1191,16 +1191,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2620</v>
+        <v>2130</v>
       </c>
       <c r="D35" t="n">
         <v>20</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>24770</v>
+        <v>22530</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -1214,16 +1214,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2820</v>
+        <v>2630</v>
       </c>
       <c r="D36" t="n">
         <v>20</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>27590</v>
+        <v>25160</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -1240,13 +1240,13 @@
         <v>200</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>3020</v>
+        <v>2830</v>
       </c>
       <c r="D37" t="n">
         <v>20</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>30610</v>
+        <v>27990</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -1263,13 +1263,13 @@
         <v>200</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>3220</v>
+        <v>3030</v>
       </c>
       <c r="D38" t="n">
         <v>20</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>33830</v>
+        <v>31020</v>
       </c>
       <c r="F38" t="n">
         <v>6</v>
@@ -1286,13 +1286,13 @@
         <v>200</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3420</v>
+        <v>3230</v>
       </c>
       <c r="D39" t="n">
         <v>20</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>37250</v>
+        <v>34250</v>
       </c>
       <c r="F39" t="n">
         <v>6</v>
@@ -1306,16 +1306,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>3720</v>
+        <v>3430</v>
       </c>
       <c r="D40" t="n">
         <v>20</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>40970</v>
+        <v>37680</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -1332,13 +1332,13 @@
         <v>300</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4020</v>
+        <v>3730</v>
       </c>
       <c r="D41" t="n">
         <v>20</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>44990</v>
+        <v>41410</v>
       </c>
       <c r="F41" t="n">
         <v>7</v>
@@ -1355,13 +1355,13 @@
         <v>300</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4320</v>
+        <v>4030</v>
       </c>
       <c r="D42" t="n">
         <v>20</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>49310</v>
+        <v>45440</v>
       </c>
       <c r="F42" t="n">
         <v>7</v>
@@ -1378,13 +1378,13 @@
         <v>300</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4620</v>
+        <v>4330</v>
       </c>
       <c r="D43" t="n">
         <v>20</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>53930</v>
+        <v>49770</v>
       </c>
       <c r="F43" t="n">
         <v>7</v>
@@ -1398,16 +1398,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>5620</v>
+        <v>4630</v>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>59550</v>
+        <v>54400</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1423,16 +1423,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>6020</v>
+        <v>5630</v>
       </c>
       <c r="D45" t="n">
         <v>30</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>65570</v>
+        <v>60030</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1448,16 +1448,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>6470</v>
+        <v>6030</v>
       </c>
       <c r="D46" t="n">
         <v>30</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>72040</v>
+        <v>66060</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1473,16 +1473,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>6970</v>
+        <v>6480</v>
       </c>
       <c r="D47" t="n">
         <v>30</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>79010</v>
+        <v>72540</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1498,16 +1498,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7520</v>
+        <v>6980</v>
       </c>
       <c r="D48" t="n">
         <v>30</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>86530</v>
+        <v>79520</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>8120</v>
+        <v>7530</v>
       </c>
       <c r="D49" t="n">
         <v>30</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>94650</v>
+        <v>87050</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1548,16 +1548,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>8770</v>
+        <v>8130</v>
       </c>
       <c r="D50" t="n">
         <v>30</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>103420</v>
+        <v>95180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1573,16 +1573,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>9470</v>
+        <v>8780</v>
       </c>
       <c r="D51" t="n">
         <v>30</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>112890</v>
+        <v>103960</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1598,16 +1598,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>10220</v>
+        <v>9480</v>
       </c>
       <c r="D52" t="n">
         <v>30</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>123110</v>
+        <v>113440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1623,16 +1623,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>11020</v>
+        <v>10230</v>
       </c>
       <c r="D53" t="n">
         <v>30</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>134130</v>
+        <v>123670</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1648,16 +1648,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="n">
-        <v>5000</v>
+        <v>800</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>16020</v>
+        <v>11030</v>
       </c>
       <c r="D54" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>150150</v>
+        <v>134700</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1673,16 +1673,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>17020</v>
+        <v>16030</v>
       </c>
       <c r="D55" t="n">
         <v>40</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>167170</v>
+        <v>150730</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>18120</v>
+        <v>17030</v>
       </c>
       <c r="D56" t="n">
         <v>40</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>185290</v>
+        <v>167760</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>19320</v>
+        <v>18130</v>
       </c>
       <c r="D57" t="n">
         <v>40</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>204610</v>
+        <v>185890</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1748,16 +1748,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>20620</v>
+        <v>19330</v>
       </c>
       <c r="D58" t="n">
         <v>40</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>225230</v>
+        <v>205220</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1773,16 +1773,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="n">
-        <v>10000</v>
+        <v>1300</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>30620</v>
+        <v>20630</v>
       </c>
       <c r="D59" t="n">
         <v>40</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>255850</v>
+        <v>225850</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1798,16 +1798,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>32120</v>
+        <v>30630</v>
       </c>
       <c r="D60" t="n">
         <v>40</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>287970</v>
+        <v>256480</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -1823,16 +1823,16 @@
         <v>57</v>
       </c>
       <c r="B61" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>34120</v>
+        <v>32130</v>
       </c>
       <c r="D61" t="n">
         <v>40</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>322090</v>
+        <v>288610</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -1848,16 +1848,16 @@
         <v>58</v>
       </c>
       <c r="B62" t="n">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>54120</v>
+        <v>34130</v>
       </c>
       <c r="D62" t="n">
         <v>40</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>376210</v>
+        <v>322740</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -1873,16 +1873,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>58120</v>
+        <v>54130</v>
       </c>
       <c r="D63" t="n">
         <v>40</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>434330</v>
+        <v>376870</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -1898,16 +1898,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>63120</v>
+        <v>58130</v>
       </c>
       <c r="D64" t="n">
         <v>40</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>497450</v>
+        <v>435000</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
